--- a/data/trans_dic/P43-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43-Habitat-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,13%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,22; 39,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,58; 50,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,09; 53,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,56; 56,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,12; 39,31</t>
+          <t>32,22; 39,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,38; 51,54</t>
+          <t>43,58; 50,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,13; 53,93</t>
+          <t>46,09; 53,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,43; 56,61</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32,12; 39,31</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>43,38; 51,54</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46,13; 53,93</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,43; 56,61</t>
+          <t>49,56; 56,9</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>35,38%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52,55%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>49,33%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,37; 38,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,06; 48,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,49; 55,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,21; 52,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 38,49</t>
+          <t>32,37; 38,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,75; 48,39</t>
+          <t>42,06; 48,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,33; 55,7</t>
+          <t>49,49; 55,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,02; 52,4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32,48; 38,49</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>41,75; 48,39</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>49,33; 55,7</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>46,02; 52,4</t>
+          <t>46,21; 52,44</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69,25%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38,93%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,25%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,1; 42,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,22; 51,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,0; 47,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,76; 85,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,27; 42,51</t>
+          <t>35,1; 42,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 51,39</t>
+          <t>44,22; 51,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,27; 47,57</t>
+          <t>40,0; 47,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55,02; 86,08</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35,27; 42,51</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43,87; 51,39</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40,27; 47,57</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>55,02; 86,08</t>
+          <t>54,76; 85,6</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48,29%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51,91%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,88%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,01; 44,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,28; 51,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,65; 55,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,82; 57,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,58; 43,99</t>
+          <t>38,01; 44,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,96; 51,56</t>
+          <t>45,28; 51,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,89; 55,39</t>
+          <t>48,65; 55,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,65; 57,77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37,58; 43,99</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>44,96; 51,56</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>48,89; 55,39</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,65; 57,77</t>
+          <t>38,82; 57,6</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>55,92%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,19; 39,57</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,44; 48,92</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,16; 51,62</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,38; 66,52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36,19; 39,57</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>45,44; 48,92</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48,16; 51,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>51,38; 66,52</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
     </row>
@@ -1344,16 +1108,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1378,22 +1141,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,20 +1160,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1455,26 +1206,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1491,10 +1222,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1509,22 +1236,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1543,26 +1270,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>587</t>
         </is>
@@ -1577,22 +1284,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1611,26 +1318,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>271231</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>243732</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>328239</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>334215</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>271231</t>
         </is>
@@ -1645,62 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>220153; 267431</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>302072; 352877</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>308018; 360149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>252976; 290441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>219435; 268582</t>
+          <t>220153; 267431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>300684; 357236</t>
+          <t>302072; 352877</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308290; 360430</t>
+          <t>308018; 360149</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>252322; 288988</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>219435; 268582</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>300684; 357236</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>308290; 360430</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>252322; 288988</t>
+          <t>252976; 290441</t>
         </is>
       </c>
     </row>
@@ -1717,22 +1384,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>419</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1751,26 +1418,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>677</t>
         </is>
@@ -1785,22 +1432,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>341470</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463929</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,26 +1466,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>362303</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>341470</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>463929</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>543552</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>362303</t>
         </is>
@@ -1853,62 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>312402; 372069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>431079; 499619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>511813; 578184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>339361; 385103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>313519; 371510</t>
+          <t>312402; 372069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>427860; 495981</t>
+          <t>431079; 499619</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>510249; 576120</t>
+          <t>511813; 578184</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>337959; 384849</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>313519; 371510</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>427860; 495981</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>510249; 576120</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>337959; 384849</t>
+          <t>339361; 385103</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1532,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1959,26 +1566,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>438</t>
         </is>
@@ -1993,22 +1580,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264087</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2027,26 +1614,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>505167</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>264087</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>370652</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>342091</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>505167</t>
         </is>
@@ -2061,62 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>238113; 288046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>342238; 398867</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>312713; 371635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>399490; 624443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>239294; 288365</t>
+          <t>238113; 288046</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>339486; 397702</t>
+          <t>342238; 398867</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>314821; 371821</t>
+          <t>312713; 371635</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>401392; 627973</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>239294; 288365</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>339486; 397702</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>314821; 371821</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>401392; 627973</t>
+          <t>399490; 624443</t>
         </is>
       </c>
     </row>
@@ -2133,22 +1680,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2167,26 +1714,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>765</t>
         </is>
@@ -2201,22 +1728,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>504428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2235,26 +1762,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>444437</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>504428</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>537442</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>444437</t>
         </is>
@@ -2269,62 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>392467; 458707</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>473042; 540009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>503752; 569585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>332508; 493374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>388097; 454226</t>
+          <t>392467; 458707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>469710; 538597</t>
+          <t>473042; 540009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>506169; 573548</t>
+          <t>503752; 569585</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>339638; 494826</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>388097; 454226</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>469710; 538597</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>506169; 573548</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>339638; 494826</t>
+          <t>332508; 493374</t>
         </is>
       </c>
     </row>
@@ -2341,22 +1828,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2375,26 +1862,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
@@ -2409,22 +1876,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1667249</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1757300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2443,26 +1910,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1583137</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1667249</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1757300</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1583137</t>
         </is>
@@ -2477,62 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1215683; 1329323</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1606844; 1729955</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1694936; 1816789</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1454515; 1883137</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1215683; 1329323</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1606844; 1729955</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1694936; 1816789</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1454515; 1883137</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
     </row>
@@ -2544,15 +1971,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P43-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43-Habitat-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,22; 39,14</t>
+          <t>32,3; 39,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,58; 50,91</t>
+          <t>43,31; 51,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,09; 53,89</t>
+          <t>46,39; 54,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,56; 56,9</t>
+          <t>48,67; 56,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,22; 39,14</t>
+          <t>32,3; 39,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,58; 50,91</t>
+          <t>43,31; 51,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,09; 53,89</t>
+          <t>46,39; 54,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,56; 56,9</t>
+          <t>48,67; 56,06</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,55</t>
+          <t>32,26; 38,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,06; 48,75</t>
+          <t>41,91; 48,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,49; 55,9</t>
+          <t>49,53; 55,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,21; 52,44</t>
+          <t>45,79; 51,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,37; 38,55</t>
+          <t>32,26; 38,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,06; 48,75</t>
+          <t>41,91; 48,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,49; 55,9</t>
+          <t>49,53; 55,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,21; 52,44</t>
+          <t>45,79; 51,85</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,1; 42,46</t>
+          <t>35,42; 43,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 51,54</t>
+          <t>44,11; 51,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 47,54</t>
+          <t>40,29; 47,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,76; 85,6</t>
+          <t>48,41; 55,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,1; 42,46</t>
+          <t>35,42; 43,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 51,54</t>
+          <t>44,11; 51,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 47,54</t>
+          <t>40,29; 47,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,76; 85,6</t>
+          <t>48,41; 55,88</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,01; 44,42</t>
+          <t>37,75; 44,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,28; 51,69</t>
+          <t>45,41; 51,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,65; 55,01</t>
+          <t>48,85; 55,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 57,6</t>
+          <t>52,39; 58,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,01; 44,42</t>
+          <t>37,75; 44,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,28; 51,69</t>
+          <t>45,41; 51,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,65; 55,01</t>
+          <t>48,85; 55,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 57,6</t>
+          <t>52,39; 58,89</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>289241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>289241</t>
         </is>
       </c>
     </row>
@@ -1332,42 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>220153; 267431</t>
+          <t>220686; 268739</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>302072; 352877</t>
+          <t>300206; 354094</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>308018; 360149</t>
+          <t>310020; 364113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252976; 290441</t>
+          <t>269127; 309991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>220153; 267431</t>
+          <t>220686; 268739</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>302072; 352877</t>
+          <t>300206; 354094</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308018; 360149</t>
+          <t>310020; 364113</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>252976; 290441</t>
+          <t>269127; 309991</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362303</t>
+          <t>401238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>362303</t>
+          <t>401238</t>
         </is>
       </c>
     </row>
@@ -1480,42 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>312402; 372069</t>
+          <t>311395; 371637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>431079; 499619</t>
+          <t>429522; 494698</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511813; 578184</t>
+          <t>512284; 575802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>339361; 385103</t>
+          <t>375294; 425018</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>312402; 372069</t>
+          <t>311395; 371637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>431079; 499619</t>
+          <t>429522; 494698</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>511813; 578184</t>
+          <t>512284; 575802</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>339361; 385103</t>
+          <t>375294; 425018</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505167</t>
+          <t>297580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>505167</t>
+          <t>297580</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>238113; 288046</t>
+          <t>240326; 292663</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>342238; 398867</t>
+          <t>341367; 396911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312713; 371635</t>
+          <t>314923; 372594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>399490; 624443</t>
+          <t>276511; 319156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>238113; 288046</t>
+          <t>240326; 292663</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>342238; 398867</t>
+          <t>341367; 396911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>312713; 371635</t>
+          <t>314923; 372594</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>399490; 624443</t>
+          <t>276511; 319156</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>444437</t>
+          <t>478434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>444437</t>
+          <t>478434</t>
         </is>
       </c>
     </row>
@@ -1776,42 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>392467; 458707</t>
+          <t>389851; 458227</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473042; 540009</t>
+          <t>474392; 536832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>503752; 569585</t>
+          <t>505782; 573453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>332508; 493374</t>
+          <t>450047; 505885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>392467; 458707</t>
+          <t>389851; 458227</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>473042; 540009</t>
+          <t>474392; 536832</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>503752; 569585</t>
+          <t>505782; 573453</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>332508; 493374</t>
+          <t>450047; 505885</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
     </row>
@@ -1924,42 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
     </row>
